--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:11</t>
+    <t xml:space="preserve">2026-09-09 23:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:05</t>
+    <t xml:space="preserve">2026-09-17 14:02</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:02</t>
+    <t xml:space="preserve">2026-09-23 12:31</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:31</t>
+    <t xml:space="preserve">2026-10-02 14:14</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
+++ b/output/graficos_dimensiones/comunal_i_ingr_a_2023_la araucania.xlsx
@@ -141,7 +141,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 14:14</t>
+    <t xml:space="preserve">2026-10-05 10:20</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -594,7 +594,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>994304.62</v>
+        <v>994304.63</v>
       </c>
     </row>
     <row r="4">
@@ -628,7 +628,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>978686.62</v>
+        <v>978686.63</v>
       </c>
     </row>
     <row r="6">
@@ -645,7 +645,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>926532.62</v>
+        <v>926532.63</v>
       </c>
     </row>
     <row r="7">
@@ -713,7 +713,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>887103.12</v>
+        <v>887103.13</v>
       </c>
     </row>
     <row r="11">
@@ -968,7 +968,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>815163.12</v>
+        <v>815163.13</v>
       </c>
     </row>
     <row r="26">
@@ -1036,7 +1036,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>772575.62</v>
+        <v>772575.63</v>
       </c>
     </row>
     <row r="30">
